--- a/数据表/Enemy.xlsx
+++ b/数据表/Enemy.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>#</t>
   </si>
@@ -43,6 +43,9 @@
     <t>MaxHealth</t>
   </si>
   <si>
+    <t>HpAddPerLevel</t>
+  </si>
+  <si>
     <t>Speed</t>
   </si>
   <si>
@@ -68,6 +71,9 @@
   </si>
   <si>
     <t>最大生命</t>
+  </si>
+  <si>
+    <t>每关卡增加生命</t>
   </si>
   <si>
     <t>移动速度</t>
@@ -1016,20 +1022,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="7"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="18.7272727272727" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.6363636363636" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.4545454545455" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.2727272727273" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.1818181818182" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.2727272727273" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.4545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.0909090909091" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.2727272727273" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1818181818182" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.2727272727273" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.4545454545455" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1037,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1059,76 +1066,88 @@
       <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I3" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="B5" s="1">
         <v>101</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1">
         <v>3</v>
       </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
       <c r="G5" s="1">
+        <v>5</v>
+      </c>
+      <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>0.3</v>
       </c>
     </row>
